--- a/human_resources_forms/021_energy_field_engineer_onboarding_form--human_resources_forms.xlsx
+++ b/human_resources_forms/021_energy_field_engineer_onboarding_form--human_resources_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_received_all_of_the_necessary_training_and_certifications_for_this_position.'}</t>
+          <t>i_have_received_all_of_the_necessary_training_and_certifications_for_this_position.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'I have received all of the necessary training and certifications for this position.'}</t>
+          <t>I have received all of the necessary training and certifications for this position.</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_completed_all_required_safety_courses.'}</t>
+          <t>i_have_completed_all_required_safety_courses.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'I have completed all required safety courses.'}</t>
+          <t>I have completed all required safety courses.</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_reviewed_and_understand_the_safety_policies_and_procedures.'}</t>
+          <t>i_have_reviewed_and_understand_the_safety_policies_and_procedures.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'I have reviewed and understand the safety policies and procedures.'}</t>
+          <t>I have reviewed and understand the safety policies and procedures.</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'i_have_received_my_safety_orientation.'}</t>
+          <t>i_have_received_my_safety_orientation.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'I have received my safety orientation.'}</t>
+          <t>I have received my safety orientation.</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'complete'}</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Complete'}</t>
+          <t>Complete</t>
         </is>
       </c>
     </row>
